--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92563797977</v>
+        <v>46157.93081355863</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93081355863</v>
+        <v>46157.93160748323</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93160748323</v>
+        <v>46157.93395670677</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93395670677</v>
+        <v>46157.93712657933</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93712657933</v>
+        <v>46158.28212344158</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28212344158</v>
+        <v>46158.29673521136</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29673521136</v>
+        <v>46158.29809094544</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29809094544</v>
+        <v>46158.33383145898</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383145898</v>
+        <v>46158.36851206567</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36851206567</v>
+        <v>46158.37283377253</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
